--- a/Plannings 2026 S21.xlsx
+++ b/Plannings 2026 S21.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F76A89A2-5C8C-43BB-810A-A43E91EB42FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{F76A89A2-5C8C-43BB-810A-A43E91EB42FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22C45F8B-D570-4703-9F47-4EE20EC3F5F7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -574,7 +574,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -607,6 +607,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -925,7 +937,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1110,6 +1122,27 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1118,6 +1151,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFCCFF"/>
       <color rgb="FFCCFFFF"/>
       <color rgb="FFCC99FF"/>
     </mruColors>
@@ -6311,7 +6345,7 @@
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="64" t="s">
         <v>14</v>
       </c>
       <c r="H7" s="22"/>
@@ -6323,7 +6357,7 @@
       <c r="D8" s="25"/>
       <c r="E8" s="25"/>
       <c r="F8" s="25"/>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="65" t="s">
         <v>15</v>
       </c>
       <c r="H8" s="26"/>
@@ -6644,7 +6678,7 @@
       <c r="C30" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="62" t="s">
         <v>14</v>
       </c>
       <c r="E30" s="19"/>
@@ -6660,7 +6694,7 @@
       <c r="C31" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="63" t="s">
         <v>49</v>
       </c>
       <c r="E31" s="2"/>
@@ -6877,7 +6911,7 @@
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
-      <c r="G44" s="3" t="s">
+      <c r="G44" s="64" t="s">
         <v>14</v>
       </c>
       <c r="H44" s="22"/>
@@ -6889,7 +6923,7 @@
       <c r="D45" s="25"/>
       <c r="E45" s="25"/>
       <c r="F45" s="25"/>
-      <c r="G45" s="25" t="s">
+      <c r="G45" s="65" t="s">
         <v>74</v>
       </c>
       <c r="H45" s="26"/>
@@ -7050,7 +7084,7 @@
       <c r="E56" s="19"/>
       <c r="F56" s="19"/>
       <c r="G56" s="19"/>
-      <c r="H56" s="20" t="s">
+      <c r="H56" s="68" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7062,7 +7096,7 @@
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
-      <c r="H57" s="22" t="s">
+      <c r="H57" s="67" t="s">
         <v>87</v>
       </c>
     </row>
@@ -7188,7 +7222,7 @@
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
-      <c r="H67" s="32" t="s">
+      <c r="H67" s="66" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7200,7 +7234,7 @@
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
-      <c r="H68" s="22" t="s">
+      <c r="H68" s="67" t="s">
         <v>94</v>
       </c>
     </row>
@@ -7260,7 +7294,7 @@
       <c r="C73" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="D73" s="19" t="s">
+      <c r="D73" s="62" t="s">
         <v>14</v>
       </c>
       <c r="E73" s="19"/>
@@ -7274,7 +7308,7 @@
       <c r="C74" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="D74" s="2" t="s">
+      <c r="D74" s="63" t="s">
         <v>98</v>
       </c>
       <c r="E74" s="2"/>
@@ -7510,7 +7544,7 @@
         <v>19</v>
       </c>
       <c r="C89" s="2"/>
-      <c r="D89" s="3" t="s">
+      <c r="D89" s="64" t="s">
         <v>14</v>
       </c>
       <c r="E89" s="2"/>
@@ -7528,7 +7562,7 @@
         <v>114</v>
       </c>
       <c r="C90" s="2"/>
-      <c r="D90" s="2" t="s">
+      <c r="D90" s="63" t="s">
         <v>115</v>
       </c>
       <c r="E90" s="2"/>
@@ -7544,10 +7578,10 @@
       <c r="A91" s="21"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
+      <c r="D91" s="63"/>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
-      <c r="G91" s="3" t="s">
+      <c r="G91" s="64" t="s">
         <v>14</v>
       </c>
       <c r="H91" s="22"/>
@@ -7556,10 +7590,10 @@
       <c r="A92" s="21"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
+      <c r="D92" s="63"/>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
-      <c r="G92" s="2" t="s">
+      <c r="G92" s="63" t="s">
         <v>118</v>
       </c>
       <c r="H92" s="22"/>
@@ -7568,7 +7602,7 @@
       <c r="A93" s="21"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
+      <c r="D93" s="63"/>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="3" t="s">
@@ -7580,7 +7614,7 @@
       <c r="A94" s="23"/>
       <c r="B94" s="25"/>
       <c r="C94" s="25"/>
-      <c r="D94" s="25"/>
+      <c r="D94" s="65"/>
       <c r="E94" s="25"/>
       <c r="F94" s="25"/>
       <c r="G94" s="25" t="s">
@@ -7681,7 +7715,7 @@
       <c r="D101" s="19"/>
       <c r="E101" s="19"/>
       <c r="F101" s="19"/>
-      <c r="G101" s="19" t="s">
+      <c r="G101" s="62" t="s">
         <v>14</v>
       </c>
       <c r="H101" s="20"/>
@@ -7693,7 +7727,7 @@
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
-      <c r="G102" s="2" t="s">
+      <c r="G102" s="63" t="s">
         <v>124</v>
       </c>
       <c r="H102" s="22"/>
@@ -8700,13 +8734,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA256E12-D58E-4CB0-A6BF-6C9C54BA964A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4442A821-9505-414A-9753-94FA89BA05D5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{627E563C-1B39-4F2A-8AA0-EA74BDF79B40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBC9276C-0F03-40F3-94EA-DEB664D2C6A7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD9D104E-E8A3-44EA-A87D-805054D515DC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AAF6256-C95F-4179-812B-DA083557110F}"/>
 </file>
--- a/Plannings 2026 S21.xlsx
+++ b/Plannings 2026 S21.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{F76A89A2-5C8C-43BB-810A-A43E91EB42FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22C45F8B-D570-4703-9F47-4EE20EC3F5F7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F76A89A2-5C8C-43BB-810A-A43E91EB42FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -574,7 +574,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -607,18 +607,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -937,7 +925,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1122,27 +1110,6 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1151,7 +1118,6 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFFFCCFF"/>
       <color rgb="FFCCFFFF"/>
       <color rgb="FFCC99FF"/>
     </mruColors>
@@ -6345,7 +6311,7 @@
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="H7" s="22"/>
@@ -6357,7 +6323,7 @@
       <c r="D8" s="25"/>
       <c r="E8" s="25"/>
       <c r="F8" s="25"/>
-      <c r="G8" s="65" t="s">
+      <c r="G8" s="25" t="s">
         <v>15</v>
       </c>
       <c r="H8" s="26"/>
@@ -6678,7 +6644,7 @@
       <c r="C30" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D30" s="62" t="s">
+      <c r="D30" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E30" s="19"/>
@@ -6694,7 +6660,7 @@
       <c r="C31" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D31" s="63" t="s">
+      <c r="D31" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E31" s="2"/>
@@ -6911,7 +6877,7 @@
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
-      <c r="G44" s="64" t="s">
+      <c r="G44" s="3" t="s">
         <v>14</v>
       </c>
       <c r="H44" s="22"/>
@@ -6923,7 +6889,7 @@
       <c r="D45" s="25"/>
       <c r="E45" s="25"/>
       <c r="F45" s="25"/>
-      <c r="G45" s="65" t="s">
+      <c r="G45" s="25" t="s">
         <v>74</v>
       </c>
       <c r="H45" s="26"/>
@@ -7084,7 +7050,7 @@
       <c r="E56" s="19"/>
       <c r="F56" s="19"/>
       <c r="G56" s="19"/>
-      <c r="H56" s="68" t="s">
+      <c r="H56" s="20" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7096,7 +7062,7 @@
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
-      <c r="H57" s="67" t="s">
+      <c r="H57" s="22" t="s">
         <v>87</v>
       </c>
     </row>
@@ -7222,7 +7188,7 @@
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
-      <c r="H67" s="66" t="s">
+      <c r="H67" s="32" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7234,7 +7200,7 @@
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
-      <c r="H68" s="67" t="s">
+      <c r="H68" s="22" t="s">
         <v>94</v>
       </c>
     </row>
@@ -7294,7 +7260,7 @@
       <c r="C73" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="D73" s="62" t="s">
+      <c r="D73" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E73" s="19"/>
@@ -7308,7 +7274,7 @@
       <c r="C74" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="D74" s="63" t="s">
+      <c r="D74" s="2" t="s">
         <v>98</v>
       </c>
       <c r="E74" s="2"/>
@@ -7544,7 +7510,7 @@
         <v>19</v>
       </c>
       <c r="C89" s="2"/>
-      <c r="D89" s="64" t="s">
+      <c r="D89" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E89" s="2"/>
@@ -7562,7 +7528,7 @@
         <v>114</v>
       </c>
       <c r="C90" s="2"/>
-      <c r="D90" s="63" t="s">
+      <c r="D90" s="2" t="s">
         <v>115</v>
       </c>
       <c r="E90" s="2"/>
@@ -7578,10 +7544,10 @@
       <c r="A91" s="21"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
-      <c r="D91" s="63"/>
+      <c r="D91" s="2"/>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
-      <c r="G91" s="64" t="s">
+      <c r="G91" s="3" t="s">
         <v>14</v>
       </c>
       <c r="H91" s="22"/>
@@ -7590,10 +7556,10 @@
       <c r="A92" s="21"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
-      <c r="D92" s="63"/>
+      <c r="D92" s="2"/>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
-      <c r="G92" s="63" t="s">
+      <c r="G92" s="2" t="s">
         <v>118</v>
       </c>
       <c r="H92" s="22"/>
@@ -7602,7 +7568,7 @@
       <c r="A93" s="21"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
-      <c r="D93" s="63"/>
+      <c r="D93" s="2"/>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="3" t="s">
@@ -7614,7 +7580,7 @@
       <c r="A94" s="23"/>
       <c r="B94" s="25"/>
       <c r="C94" s="25"/>
-      <c r="D94" s="65"/>
+      <c r="D94" s="25"/>
       <c r="E94" s="25"/>
       <c r="F94" s="25"/>
       <c r="G94" s="25" t="s">
@@ -7715,7 +7681,7 @@
       <c r="D101" s="19"/>
       <c r="E101" s="19"/>
       <c r="F101" s="19"/>
-      <c r="G101" s="62" t="s">
+      <c r="G101" s="19" t="s">
         <v>14</v>
       </c>
       <c r="H101" s="20"/>
@@ -7727,7 +7693,7 @@
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
-      <c r="G102" s="63" t="s">
+      <c r="G102" s="2" t="s">
         <v>124</v>
       </c>
       <c r="H102" s="22"/>
@@ -8734,13 +8700,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4442A821-9505-414A-9753-94FA89BA05D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA256E12-D58E-4CB0-A6BF-6C9C54BA964A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBC9276C-0F03-40F3-94EA-DEB664D2C6A7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{627E563C-1B39-4F2A-8AA0-EA74BDF79B40}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AAF6256-C95F-4179-812B-DA083557110F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD9D104E-E8A3-44EA-A87D-805054D515DC}"/>
 </file>
--- a/Plannings 2026 S21.xlsx
+++ b/Plannings 2026 S21.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{F76A89A2-5C8C-43BB-810A-A43E91EB42FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22C45F8B-D570-4703-9F47-4EE20EC3F5F7}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{F76A89A2-5C8C-43BB-810A-A43E91EB42FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF09780E-C98D-4079-AC93-E3C7CED892AE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -937,7 +937,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1141,6 +1141,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6367,7 +6376,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="19"/>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="69" t="s">
         <v>17</v>
       </c>
       <c r="D9" s="19"/>
@@ -6379,7 +6388,7 @@
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="21"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="70" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="2"/>
@@ -6556,7 +6565,7 @@
       </c>
       <c r="B22" s="19"/>
       <c r="C22" s="19"/>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="69" t="s">
         <v>17</v>
       </c>
       <c r="E22" s="19"/>
@@ -6568,7 +6577,7 @@
       <c r="A23" s="21"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="70" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="2"/>
@@ -6675,7 +6684,7 @@
         <v>46</v>
       </c>
       <c r="B30" s="19"/>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="69" t="s">
         <v>17</v>
       </c>
       <c r="D30" s="62" t="s">
@@ -6691,7 +6700,7 @@
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="21"/>
       <c r="B31" s="2"/>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="70" t="s">
         <v>48</v>
       </c>
       <c r="D31" s="63" t="s">
@@ -6932,7 +6941,7 @@
       <c r="A46" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="B46" s="19" t="s">
+      <c r="B46" s="44" t="s">
         <v>12</v>
       </c>
       <c r="C46" s="19"/>
@@ -6952,7 +6961,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="21"/>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="46" t="s">
         <v>77</v>
       </c>
       <c r="C47" s="2"/>
@@ -7500,7 +7509,7 @@
       <c r="A87" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="B87" s="2" t="s">
+      <c r="B87" s="60" t="s">
         <v>56</v>
       </c>
       <c r="C87" s="2"/>
@@ -7520,7 +7529,7 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="21"/>
-      <c r="B88" s="2" t="s">
+      <c r="B88" s="60" t="s">
         <v>111</v>
       </c>
       <c r="C88" s="2"/>
@@ -7796,7 +7805,7 @@
       <c r="A108" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="B108" s="19" t="s">
+      <c r="B108" s="71" t="s">
         <v>17</v>
       </c>
       <c r="C108" s="19"/>
@@ -7810,7 +7819,7 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="21"/>
-      <c r="B109" s="2" t="s">
+      <c r="B109" s="70" t="s">
         <v>127</v>
       </c>
       <c r="C109" s="2"/>
@@ -8734,13 +8743,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4442A821-9505-414A-9753-94FA89BA05D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C48E8A6-6CE9-4D56-B0E6-C4D0BAD50C7A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBC9276C-0F03-40F3-94EA-DEB664D2C6A7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BAEA36B-7FF9-4808-B9A9-2A250B4DC3CD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AAF6256-C95F-4179-812B-DA083557110F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5638B6DF-1536-4317-A35B-077629E1FA52}"/>
 </file>
--- a/Plannings 2026 S21.xlsx
+++ b/Plannings 2026 S21.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{F76A89A2-5C8C-43BB-810A-A43E91EB42FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF09780E-C98D-4079-AC93-E3C7CED892AE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F76A89A2-5C8C-43BB-810A-A43E91EB42FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -574,7 +574,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -607,18 +607,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -937,7 +925,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1122,36 +1110,6 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1160,7 +1118,6 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFFFCCFF"/>
       <color rgb="FFCCFFFF"/>
       <color rgb="FFCC99FF"/>
     </mruColors>
@@ -6354,7 +6311,7 @@
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="H7" s="22"/>
@@ -6366,7 +6323,7 @@
       <c r="D8" s="25"/>
       <c r="E8" s="25"/>
       <c r="F8" s="25"/>
-      <c r="G8" s="65" t="s">
+      <c r="G8" s="25" t="s">
         <v>15</v>
       </c>
       <c r="H8" s="26"/>
@@ -6376,7 +6333,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="19"/>
-      <c r="C9" s="69" t="s">
+      <c r="C9" s="19" t="s">
         <v>17</v>
       </c>
       <c r="D9" s="19"/>
@@ -6388,7 +6345,7 @@
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="21"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="70" t="s">
+      <c r="C10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="2"/>
@@ -6565,7 +6522,7 @@
       </c>
       <c r="B22" s="19"/>
       <c r="C22" s="19"/>
-      <c r="D22" s="69" t="s">
+      <c r="D22" s="19" t="s">
         <v>17</v>
       </c>
       <c r="E22" s="19"/>
@@ -6577,7 +6534,7 @@
       <c r="A23" s="21"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
-      <c r="D23" s="70" t="s">
+      <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="2"/>
@@ -6684,10 +6641,10 @@
         <v>46</v>
       </c>
       <c r="B30" s="19"/>
-      <c r="C30" s="69" t="s">
+      <c r="C30" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D30" s="62" t="s">
+      <c r="D30" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E30" s="19"/>
@@ -6700,10 +6657,10 @@
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="21"/>
       <c r="B31" s="2"/>
-      <c r="C31" s="70" t="s">
+      <c r="C31" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D31" s="63" t="s">
+      <c r="D31" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E31" s="2"/>
@@ -6920,7 +6877,7 @@
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
-      <c r="G44" s="64" t="s">
+      <c r="G44" s="3" t="s">
         <v>14</v>
       </c>
       <c r="H44" s="22"/>
@@ -6932,7 +6889,7 @@
       <c r="D45" s="25"/>
       <c r="E45" s="25"/>
       <c r="F45" s="25"/>
-      <c r="G45" s="65" t="s">
+      <c r="G45" s="25" t="s">
         <v>74</v>
       </c>
       <c r="H45" s="26"/>
@@ -6941,7 +6898,7 @@
       <c r="A46" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="B46" s="44" t="s">
+      <c r="B46" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C46" s="19"/>
@@ -6961,7 +6918,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="21"/>
-      <c r="B47" s="46" t="s">
+      <c r="B47" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C47" s="2"/>
@@ -7093,7 +7050,7 @@
       <c r="E56" s="19"/>
       <c r="F56" s="19"/>
       <c r="G56" s="19"/>
-      <c r="H56" s="68" t="s">
+      <c r="H56" s="20" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7105,7 +7062,7 @@
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
-      <c r="H57" s="67" t="s">
+      <c r="H57" s="22" t="s">
         <v>87</v>
       </c>
     </row>
@@ -7231,7 +7188,7 @@
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
-      <c r="H67" s="66" t="s">
+      <c r="H67" s="32" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7243,7 +7200,7 @@
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
-      <c r="H68" s="67" t="s">
+      <c r="H68" s="22" t="s">
         <v>94</v>
       </c>
     </row>
@@ -7303,7 +7260,7 @@
       <c r="C73" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="D73" s="62" t="s">
+      <c r="D73" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E73" s="19"/>
@@ -7317,7 +7274,7 @@
       <c r="C74" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="D74" s="63" t="s">
+      <c r="D74" s="2" t="s">
         <v>98</v>
       </c>
       <c r="E74" s="2"/>
@@ -7509,7 +7466,7 @@
       <c r="A87" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="B87" s="60" t="s">
+      <c r="B87" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C87" s="2"/>
@@ -7529,7 +7486,7 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="21"/>
-      <c r="B88" s="60" t="s">
+      <c r="B88" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C88" s="2"/>
@@ -7553,7 +7510,7 @@
         <v>19</v>
       </c>
       <c r="C89" s="2"/>
-      <c r="D89" s="64" t="s">
+      <c r="D89" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E89" s="2"/>
@@ -7571,7 +7528,7 @@
         <v>114</v>
       </c>
       <c r="C90" s="2"/>
-      <c r="D90" s="63" t="s">
+      <c r="D90" s="2" t="s">
         <v>115</v>
       </c>
       <c r="E90" s="2"/>
@@ -7587,10 +7544,10 @@
       <c r="A91" s="21"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
-      <c r="D91" s="63"/>
+      <c r="D91" s="2"/>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
-      <c r="G91" s="64" t="s">
+      <c r="G91" s="3" t="s">
         <v>14</v>
       </c>
       <c r="H91" s="22"/>
@@ -7599,10 +7556,10 @@
       <c r="A92" s="21"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
-      <c r="D92" s="63"/>
+      <c r="D92" s="2"/>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
-      <c r="G92" s="63" t="s">
+      <c r="G92" s="2" t="s">
         <v>118</v>
       </c>
       <c r="H92" s="22"/>
@@ -7611,7 +7568,7 @@
       <c r="A93" s="21"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
-      <c r="D93" s="63"/>
+      <c r="D93" s="2"/>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="3" t="s">
@@ -7623,7 +7580,7 @@
       <c r="A94" s="23"/>
       <c r="B94" s="25"/>
       <c r="C94" s="25"/>
-      <c r="D94" s="65"/>
+      <c r="D94" s="25"/>
       <c r="E94" s="25"/>
       <c r="F94" s="25"/>
       <c r="G94" s="25" t="s">
@@ -7724,7 +7681,7 @@
       <c r="D101" s="19"/>
       <c r="E101" s="19"/>
       <c r="F101" s="19"/>
-      <c r="G101" s="62" t="s">
+      <c r="G101" s="19" t="s">
         <v>14</v>
       </c>
       <c r="H101" s="20"/>
@@ -7736,7 +7693,7 @@
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
-      <c r="G102" s="63" t="s">
+      <c r="G102" s="2" t="s">
         <v>124</v>
       </c>
       <c r="H102" s="22"/>
@@ -7805,7 +7762,7 @@
       <c r="A108" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="B108" s="71" t="s">
+      <c r="B108" s="19" t="s">
         <v>17</v>
       </c>
       <c r="C108" s="19"/>
@@ -7819,7 +7776,7 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="21"/>
-      <c r="B109" s="70" t="s">
+      <c r="B109" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C109" s="2"/>
@@ -8743,13 +8700,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C48E8A6-6CE9-4D56-B0E6-C4D0BAD50C7A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA256E12-D58E-4CB0-A6BF-6C9C54BA964A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BAEA36B-7FF9-4808-B9A9-2A250B4DC3CD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{627E563C-1B39-4F2A-8AA0-EA74BDF79B40}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5638B6DF-1536-4317-A35B-077629E1FA52}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD9D104E-E8A3-44EA-A87D-805054D515DC}"/>
 </file>
--- a/Plannings 2026 S21.xlsx
+++ b/Plannings 2026 S21.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{F76A89A2-5C8C-43BB-810A-A43E91EB42FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF09780E-C98D-4079-AC93-E3C7CED892AE}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{F76A89A2-5C8C-43BB-810A-A43E91EB42FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BFFDCAE-5725-4157-9384-DB40305DEFE0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="150">
   <si>
     <t>Planning des salariés du 18/05/2026 au 24/05/2026</t>
   </si>
@@ -466,6 +466,12 @@
   </si>
   <si>
     <t>FORP Anniv</t>
+  </si>
+  <si>
+    <t>P50 // C. PADEL // EDF // LEAGUES</t>
+  </si>
+  <si>
+    <t>C. PADEL // EDF // LEAGUES</t>
   </si>
 </sst>
 </file>
@@ -6287,8 +6293,12 @@
       <c r="H2" s="13"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
+      <c r="B3" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>149</v>
+      </c>
       <c r="D3" s="16"/>
       <c r="E3" s="16"/>
       <c r="F3" s="16"/>
@@ -8743,13 +8753,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C48E8A6-6CE9-4D56-B0E6-C4D0BAD50C7A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8B23379-F429-4EBB-A5EA-2588D2A3D75A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BAEA36B-7FF9-4808-B9A9-2A250B4DC3CD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A03C9624-6347-41BA-942E-CB3754D6CDE0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5638B6DF-1536-4317-A35B-077629E1FA52}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{877B797F-571B-4E3C-8E29-78C42E6DFA50}"/>
 </file>
--- a/Plannings 2026 S21.xlsx
+++ b/Plannings 2026 S21.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{F76A89A2-5C8C-43BB-810A-A43E91EB42FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3BFFDCAE-5725-4157-9384-DB40305DEFE0}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{F76A89A2-5C8C-43BB-810A-A43E91EB42FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5F26C98-72EC-4551-9838-2A09EB5A20E9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="153">
   <si>
     <t>Planning des salariés du 18/05/2026 au 24/05/2026</t>
   </si>
@@ -472,6 +472,15 @@
   </si>
   <si>
     <t>C. PADEL // EDF // LEAGUES</t>
+  </si>
+  <si>
+    <t>C. PADEL</t>
+  </si>
+  <si>
+    <t>P500 // EDF // ANNIV</t>
+  </si>
+  <si>
+    <t>EVENT VERISURE en attente // C. PADEL // EDF</t>
   </si>
 </sst>
 </file>
@@ -6299,11 +6308,21 @@
       <c r="C3" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
+      <c r="D3" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
@@ -8753,13 +8772,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8B23379-F429-4EBB-A5EA-2588D2A3D75A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56BCB3AC-1B8B-4A38-A13B-6BEFEF25800E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A03C9624-6347-41BA-942E-CB3754D6CDE0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73030B45-1BE2-43E4-812D-B84A1F1E426B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{877B797F-571B-4E3C-8E29-78C42E6DFA50}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4CFA7FA-97A2-4569-A88E-9A027EB17BFC}"/>
 </file>
--- a/Plannings 2026 S21.xlsx
+++ b/Plannings 2026 S21.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdalpes.sharepoint.com/sites/msteams_bd0f90/Documents partages/02. USP - TOS - General/RH/Plannings/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{F76A89A2-5C8C-43BB-810A-A43E91EB42FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5F26C98-72EC-4551-9838-2A09EB5A20E9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F76A89A2-5C8C-43BB-810A-A43E91EB42FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="148">
   <si>
     <t>Planning des salariés du 18/05/2026 au 24/05/2026</t>
   </si>
@@ -466,21 +466,6 @@
   </si>
   <si>
     <t>FORP Anniv</t>
-  </si>
-  <si>
-    <t>P50 // C. PADEL // EDF // LEAGUES</t>
-  </si>
-  <si>
-    <t>C. PADEL // EDF // LEAGUES</t>
-  </si>
-  <si>
-    <t>C. PADEL</t>
-  </si>
-  <si>
-    <t>P500 // EDF // ANNIV</t>
-  </si>
-  <si>
-    <t>EVENT VERISURE en attente // C. PADEL // EDF</t>
   </si>
 </sst>
 </file>
@@ -589,7 +574,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -622,18 +607,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCCFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -952,7 +925,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1137,36 +1110,6 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1175,7 +1118,6 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFFFCCFF"/>
       <color rgb="FFCCFFFF"/>
       <color rgb="FFCC99FF"/>
     </mruColors>
@@ -6302,27 +6244,13 @@
       <c r="H2" s="13"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="H3" s="16" t="s">
-        <v>47</v>
-      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
@@ -6383,7 +6311,7 @@
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="H7" s="22"/>
@@ -6395,7 +6323,7 @@
       <c r="D8" s="25"/>
       <c r="E8" s="25"/>
       <c r="F8" s="25"/>
-      <c r="G8" s="65" t="s">
+      <c r="G8" s="25" t="s">
         <v>15</v>
       </c>
       <c r="H8" s="26"/>
@@ -6405,7 +6333,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="19"/>
-      <c r="C9" s="69" t="s">
+      <c r="C9" s="19" t="s">
         <v>17</v>
       </c>
       <c r="D9" s="19"/>
@@ -6417,7 +6345,7 @@
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="21"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="70" t="s">
+      <c r="C10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="2"/>
@@ -6594,7 +6522,7 @@
       </c>
       <c r="B22" s="19"/>
       <c r="C22" s="19"/>
-      <c r="D22" s="69" t="s">
+      <c r="D22" s="19" t="s">
         <v>17</v>
       </c>
       <c r="E22" s="19"/>
@@ -6606,7 +6534,7 @@
       <c r="A23" s="21"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
-      <c r="D23" s="70" t="s">
+      <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="2"/>
@@ -6713,10 +6641,10 @@
         <v>46</v>
       </c>
       <c r="B30" s="19"/>
-      <c r="C30" s="69" t="s">
+      <c r="C30" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D30" s="62" t="s">
+      <c r="D30" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E30" s="19"/>
@@ -6729,10 +6657,10 @@
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="21"/>
       <c r="B31" s="2"/>
-      <c r="C31" s="70" t="s">
+      <c r="C31" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D31" s="63" t="s">
+      <c r="D31" s="2" t="s">
         <v>49</v>
       </c>
       <c r="E31" s="2"/>
@@ -6949,7 +6877,7 @@
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
-      <c r="G44" s="64" t="s">
+      <c r="G44" s="3" t="s">
         <v>14</v>
       </c>
       <c r="H44" s="22"/>
@@ -6961,7 +6889,7 @@
       <c r="D45" s="25"/>
       <c r="E45" s="25"/>
       <c r="F45" s="25"/>
-      <c r="G45" s="65" t="s">
+      <c r="G45" s="25" t="s">
         <v>74</v>
       </c>
       <c r="H45" s="26"/>
@@ -6970,7 +6898,7 @@
       <c r="A46" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="B46" s="44" t="s">
+      <c r="B46" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C46" s="19"/>
@@ -6990,7 +6918,7 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="21"/>
-      <c r="B47" s="46" t="s">
+      <c r="B47" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C47" s="2"/>
@@ -7122,7 +7050,7 @@
       <c r="E56" s="19"/>
       <c r="F56" s="19"/>
       <c r="G56" s="19"/>
-      <c r="H56" s="68" t="s">
+      <c r="H56" s="20" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7134,7 +7062,7 @@
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
-      <c r="H57" s="67" t="s">
+      <c r="H57" s="22" t="s">
         <v>87</v>
       </c>
     </row>
@@ -7260,7 +7188,7 @@
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
-      <c r="H67" s="66" t="s">
+      <c r="H67" s="32" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7272,7 +7200,7 @@
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
-      <c r="H68" s="67" t="s">
+      <c r="H68" s="22" t="s">
         <v>94</v>
       </c>
     </row>
@@ -7332,7 +7260,7 @@
       <c r="C73" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="D73" s="62" t="s">
+      <c r="D73" s="19" t="s">
         <v>14</v>
       </c>
       <c r="E73" s="19"/>
@@ -7346,7 +7274,7 @@
       <c r="C74" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="D74" s="63" t="s">
+      <c r="D74" s="2" t="s">
         <v>98</v>
       </c>
       <c r="E74" s="2"/>
@@ -7538,7 +7466,7 @@
       <c r="A87" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="B87" s="60" t="s">
+      <c r="B87" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C87" s="2"/>
@@ -7558,7 +7486,7 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="21"/>
-      <c r="B88" s="60" t="s">
+      <c r="B88" s="2" t="s">
         <v>111</v>
       </c>
       <c r="C88" s="2"/>
@@ -7582,7 +7510,7 @@
         <v>19</v>
       </c>
       <c r="C89" s="2"/>
-      <c r="D89" s="64" t="s">
+      <c r="D89" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E89" s="2"/>
@@ -7600,7 +7528,7 @@
         <v>114</v>
       </c>
       <c r="C90" s="2"/>
-      <c r="D90" s="63" t="s">
+      <c r="D90" s="2" t="s">
         <v>115</v>
       </c>
       <c r="E90" s="2"/>
@@ -7616,10 +7544,10 @@
       <c r="A91" s="21"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
-      <c r="D91" s="63"/>
+      <c r="D91" s="2"/>
       <c r="E91" s="2"/>
       <c r="F91" s="2"/>
-      <c r="G91" s="64" t="s">
+      <c r="G91" s="3" t="s">
         <v>14</v>
       </c>
       <c r="H91" s="22"/>
@@ -7628,10 +7556,10 @@
       <c r="A92" s="21"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
-      <c r="D92" s="63"/>
+      <c r="D92" s="2"/>
       <c r="E92" s="2"/>
       <c r="F92" s="2"/>
-      <c r="G92" s="63" t="s">
+      <c r="G92" s="2" t="s">
         <v>118</v>
       </c>
       <c r="H92" s="22"/>
@@ -7640,7 +7568,7 @@
       <c r="A93" s="21"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
-      <c r="D93" s="63"/>
+      <c r="D93" s="2"/>
       <c r="E93" s="2"/>
       <c r="F93" s="2"/>
       <c r="G93" s="3" t="s">
@@ -7652,7 +7580,7 @@
       <c r="A94" s="23"/>
       <c r="B94" s="25"/>
       <c r="C94" s="25"/>
-      <c r="D94" s="65"/>
+      <c r="D94" s="25"/>
       <c r="E94" s="25"/>
       <c r="F94" s="25"/>
       <c r="G94" s="25" t="s">
@@ -7753,7 +7681,7 @@
       <c r="D101" s="19"/>
       <c r="E101" s="19"/>
       <c r="F101" s="19"/>
-      <c r="G101" s="62" t="s">
+      <c r="G101" s="19" t="s">
         <v>14</v>
       </c>
       <c r="H101" s="20"/>
@@ -7765,7 +7693,7 @@
       <c r="D102" s="2"/>
       <c r="E102" s="2"/>
       <c r="F102" s="2"/>
-      <c r="G102" s="63" t="s">
+      <c r="G102" s="2" t="s">
         <v>124</v>
       </c>
       <c r="H102" s="22"/>
@@ -7834,7 +7762,7 @@
       <c r="A108" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="B108" s="71" t="s">
+      <c r="B108" s="19" t="s">
         <v>17</v>
       </c>
       <c r="C108" s="19"/>
@@ -7848,7 +7776,7 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="21"/>
-      <c r="B109" s="70" t="s">
+      <c r="B109" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C109" s="2"/>
@@ -8772,13 +8700,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56BCB3AC-1B8B-4A38-A13B-6BEFEF25800E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA256E12-D58E-4CB0-A6BF-6C9C54BA964A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73030B45-1BE2-43E4-812D-B84A1F1E426B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{627E563C-1B39-4F2A-8AA0-EA74BDF79B40}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4CFA7FA-97A2-4569-A88E-9A027EB17BFC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD9D104E-E8A3-44EA-A87D-805054D515DC}"/>
 </file>